--- a/data/trans_orig/P20B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>41213</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39036</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55203</t>
+          <t>55340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58846</t>
+          <t>59250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77575</t>
+          <t>77728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104970</t>
+          <t>106416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127524</t>
+          <t>127852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28957</t>
+          <t>28564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>39838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92440</t>
+          <t>92406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106011</t>
+          <t>106130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125854</t>
+          <t>125523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143393</t>
+          <t>143147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>49599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185435</t>
+          <t>186288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209426</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>279911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312398</t>
+          <t>310803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>38039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54177</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80112</t>
+          <t>79915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83741</t>
+          <t>83345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106335</t>
+          <t>106237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151271</t>
+          <t>153305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179869</t>
+          <t>181522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>50325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77890</t>
+          <t>78546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>55054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112016</t>
+          <t>113226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134287</t>
+          <t>134378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174641</t>
+          <t>173985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201022</t>
+          <t>202206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36848</t>
+          <t>36923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48867</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77139</t>
+          <t>76402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98443</t>
+          <t>98841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122549</t>
+          <t>122841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163842</t>
+          <t>165369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129899</t>
+          <t>130636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158815</t>
+          <t>158743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236093</t>
+          <t>235695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268412</t>
+          <t>267802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377732</t>
+          <t>376205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419025</t>
+          <t>418733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016 (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>40254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59121</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31879</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45179</t>
+          <t>45454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60721</t>
+          <t>60429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78663</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101310</t>
+          <t>102341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25458</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>43888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45657</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>53425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81961</t>
+          <t>81328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37682</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55646</t>
+          <t>56433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95973</t>
+          <t>96319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118274</t>
+          <t>117591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140774</t>
+          <t>141407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168593</t>
+          <t>169310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39199</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>58231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>69088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>50800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>81415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96117</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119975</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189684</t>
+          <t>188116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>217828</t>
+          <t>218731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291088</t>
+          <t>289558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330762</t>
+          <t>329585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>40728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42805</t>
+          <t>42323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37519</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>46773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70941</t>
+          <t>70833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>86255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>24774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>43150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>48620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75260</t>
+          <t>74915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52893</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71048</t>
+          <t>69992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77619</t>
+          <t>78458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95554</t>
+          <t>95619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135961</t>
+          <t>136306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162487</t>
+          <t>162601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>31596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31874</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54071</t>
+          <t>54017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69475</t>
+          <t>68746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75338</t>
+          <t>75286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62506</t>
+          <t>60877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95483</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>130718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112018</t>
+          <t>112070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136941</t>
+          <t>137011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154171</t>
+          <t>155800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177441</t>
+          <t>176966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275037</t>
+          <t>273315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308550</t>
+          <t>307653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>31813</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23747</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40829</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>40,64%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>49035</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>38442</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>61653</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>37,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31813</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22735</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41213</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>22,63%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>41,02%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>49035</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>38708</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>60144</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55340</t>
+          <t>55336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>62,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>68650</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59634</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76716</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>68,33%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>59,36%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>117525</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>104907</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>128118</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>62,98%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68650</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59250</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77728</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,33%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>58,98%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>77,37%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>117525</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>106416</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>127852</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>70,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>63,89%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33548</t>
+          <t>32321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28564</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39838</t>
+          <t>40148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>90964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106130</t>
+          <t>105822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125523</t>
+          <t>126750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143147</t>
+          <t>143271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32863</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>35899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49599</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71546</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88128</t>
+          <t>88556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>209743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279911</t>
+          <t>279846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>311987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38039</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>29041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>50285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>53891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80741</t>
+          <t>82767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61157</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79915</t>
+          <t>79096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83345</t>
+          <t>84565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106237</t>
+          <t>105809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153305</t>
+          <t>151279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181522</t>
+          <t>180155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45084</t>
+          <t>45403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50325</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78546</t>
+          <t>78802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55054</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72514</t>
+          <t>72853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>112907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134378</t>
+          <t>133566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173985</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202206</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48606</t>
+          <t>48699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48295</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76402</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98841</t>
+          <t>99595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122841</t>
+          <t>122778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165369</t>
+          <t>162727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130636</t>
+          <t>132135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158743</t>
+          <t>160006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235695</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>267802</t>
+          <t>267261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376205</t>
+          <t>378847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>418733</t>
+          <t>418796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35443</t>
+          <t>35808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58829</t>
+          <t>57853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>45374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>42224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60429</t>
+          <t>60452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78955</t>
+          <t>79931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102341</t>
+          <t>101976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43888</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>24372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53425</t>
+          <t>55256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81328</t>
+          <t>82183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56433</t>
+          <t>56265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96319</t>
+          <t>96190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117591</t>
+          <t>117258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141407</t>
+          <t>140552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169310</t>
+          <t>167479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>58305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69088</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50800</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102423</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>140282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95274</t>
+          <t>93986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>119183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218731</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289558</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>329585</t>
+          <t>330203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,22 +5607,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>45348</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36858</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46773</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>79319</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70833</t>
+          <t>75260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86255</t>
+          <t>91803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>58237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>58237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>58237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>118735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>118735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>118735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43150</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>42542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48620</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74915</t>
+          <t>84705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>61947</t>
+          <t>68035</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51616</t>
+          <t>57155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>77278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87964</t>
+          <t>102370</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78458</t>
+          <t>92073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95619</t>
+          <t>111421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>149910</t>
+          <t>170405</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136306</t>
+          <t>155498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162601</t>
+          <t>183543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116455</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116455</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116455</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>240203</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>240203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>240203</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>28662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>29298</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31596</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>40463</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32150</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54017</t>
+          <t>61623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68746</t>
+          <t>76443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50345</t>
+          <t>55924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75286</t>
+          <t>82413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60877</t>
+          <t>69364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124932</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96380</t>
+          <t>106826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130718</t>
+          <t>145543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125079</t>
+          <t>136109</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112070</t>
+          <t>121898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>148387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167000</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155800</t>
+          <t>175549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176966</t>
+          <t>199937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>292079</t>
+          <t>324291</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273315</t>
+          <t>303680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307653</t>
+          <t>342397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>187356</t>
+          <t>204311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>187356</t>
+          <t>204311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>187356</t>
+          <t>204311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>216677</t>
+          <t>244913</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>216677</t>
+          <t>244913</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>216677</t>
+          <t>244913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>404033</t>
+          <t>449223</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>404033</t>
+          <t>449223</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>404033</t>
+          <t>449223</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
